--- a/homeworks/zippass_optimized/report/hoja_de_calculo.xlsx
+++ b/homeworks/zippass_optimized/report/hoja_de_calculo.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Optimización: zippass_serial</t>
   </si>
@@ -54,6 +54,9 @@
     <t>Eficiencia:</t>
   </si>
   <si>
+    <t>1.0565/1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Optimización: zippass_pthreads</t>
   </si>
   <si>
@@ -109,6 +112,30 @@
   </si>
   <si>
     <t xml:space="preserve">3.20 veces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparación grado de concurrencia</t>
+  </si>
+  <si>
+    <t>1C</t>
+  </si>
+  <si>
+    <t>2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.08  segundos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.325 veces</t>
+  </si>
+  <si>
+    <t>4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.734  segundos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91 veces</t>
   </si>
 </sst>
 </file>
@@ -149,11 +176,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -166,6 +190,12 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -686,53 +716,53 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -740,110 +770,110 @@
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2">
-        <v>1.0565</v>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C9" s="6">
         <v>1.0569</v>
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="5"/>
+      <c r="A12" s="4"/>
       <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="5"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="4"/>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.42599999999999999</v>
       </c>
       <c r="C19" s="6">
         <v>0.28999999999999998</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="4"/>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.45000000000000001</v>
       </c>
       <c r="C21" s="6">
@@ -851,95 +881,332 @@
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="5"/>
+      <c r="A24" s="4"/>
       <c r="B24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="1"/>
+      <c r="B26" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="5"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="2" t="s">
-        <v>18</v>
+      <c r="A29" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="2">
+      <c r="A30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="1">
         <v>0.44</v>
       </c>
       <c r="C30" s="6">
         <v>0.40000000000000002</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="5"/>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" ht="14.25"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="1">
+        <v>1</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="1"/>
+    </row>
+    <row r="39" ht="14.25"/>
+    <row r="40" ht="14.25">
+      <c r="A40" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.40999999999999998</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" s="5"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="6"/>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="6"/>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="6"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B32:D32"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/homeworks/zippass_optimized/report/hoja_de_calculo.xlsx
+++ b/homeworks/zippass_optimized/report/hoja_de_calculo.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Optimización: zippass_serial</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Eficiencia:</t>
   </si>
   <si>
-    <t>1.0565/1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Optimización: zippass_pthreads</t>
   </si>
   <si>
@@ -115,6 +112,15 @@
   </si>
   <si>
     <t xml:space="preserve">Comparación grado de concurrencia</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.920 segundos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98 veces</t>
   </si>
   <si>
     <t>1C</t>
@@ -176,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -198,6 +204,10 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -773,17 +783,13 @@
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1.0569</v>
-      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="4"/>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -809,10 +815,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -821,10 +827,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -836,48 +842,48 @@
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>0.42599999999999999</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="C19" s="6">
-        <v>0.28999999999999998</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="D19" s="4"/>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="1">
-        <v>0.45000000000000001</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="C21" s="6">
-        <v>0.29999999999999999</v>
+        <v>0.59999999999999998</v>
       </c>
     </row>
     <row r="23" ht="14.25">
@@ -889,7 +895,7 @@
     <row r="24" ht="14.25">
       <c r="A24" s="4"/>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -912,13 +918,13 @@
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D27" s="4"/>
     </row>
@@ -930,25 +936,25 @@
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D29" s="4"/>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" s="1">
-        <v>0.44</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="C30" s="6">
-        <v>0.40000000000000002</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="D30" s="4"/>
     </row>
@@ -961,7 +967,7 @@
     <row r="32" ht="14.25">
       <c r="A32" s="7"/>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -994,7 +1000,7 @@
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
@@ -1002,69 +1008,59 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1"/>
     </row>
-    <row r="39" ht="14.25"/>
+    <row r="39" ht="14.25">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+    </row>
     <row r="40" ht="14.25">
       <c r="A40" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B43" s="1">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" ht="14.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-    </row>
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+    </row>
+    <row r="44" ht="14.25"/>
     <row r="45" ht="14.25">
       <c r="A45" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="6"/>
@@ -1081,10 +1077,10 @@
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="6"/>
@@ -1093,10 +1089,10 @@
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B48" s="1">
-        <v>0.40999999999999998</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -1113,10 +1109,10 @@
     </row>
     <row r="50" ht="14.25">
       <c r="A50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="6"/>
@@ -1133,10 +1129,10 @@
     </row>
     <row r="52" ht="14.25">
       <c r="A52" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="6"/>
@@ -1145,41 +1141,63 @@
     </row>
     <row r="53" ht="14.25">
       <c r="A53" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B53" s="1">
-        <v>0.35999999999999999</v>
+        <v>0.40999999999999998</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
     </row>
     <row r="54" ht="14.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="5"/>
-      <c r="B55" s="1"/>
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="C55" s="1"/>
       <c r="D55" s="6"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
     </row>
     <row r="56" ht="14.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="6"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
+      <c r="A57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="C57" s="1"/>
       <c r="D57" s="6"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
+      <c r="A58" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="1">
+        <v>0.17999999999999999</v>
+      </c>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
     </row>
@@ -1190,16 +1208,46 @@
       <c r="D59" s="1"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="1"/>
+      <c r="A60" s="5"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
+      <c r="D60" s="6"/>
     </row>
     <row r="61" ht="14.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
+      <c r="D61" s="6"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="6"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
